--- a/output/india/bengaluru/urgent-care/leads.xlsx
+++ b/output/india/bengaluru/urgent-care/leads.xlsx
@@ -1,127 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="leads" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
-  <si>
-    <t>shop_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>source_website</t>
-  </si>
-  <si>
-    <t>generated_website</t>
-  </si>
-  <si>
-    <t>instagram</t>
-  </si>
-  <si>
-    <t>facebook</t>
-  </si>
-  <si>
-    <t>linkedin</t>
-  </si>
-  <si>
-    <t>twitter</t>
-  </si>
-  <si>
-    <t>social_media_links</t>
-  </si>
-  <si>
-    <t>google_maps_url</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>build_status</t>
-  </si>
-  <si>
-    <t>template_used</t>
-  </si>
-  <si>
-    <t>deployed_at</t>
-  </si>
-  <si>
-    <t>SHOP_BD5ABDA4EE</t>
-  </si>
-  <si>
-    <t>Jai Hanuman Ambulance Service</t>
-  </si>
-  <si>
-    <t>097408 02690</t>
-  </si>
-  <si>
-    <t>info@jaihanumanambulance.com</t>
-  </si>
-  <si>
-    <t>https://www.jaihanumanambulance.com/</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Jai+Hanuman+Ambulance+Service/@13.023504,77.3923544,12z/data=!4m9!1m2!2m1!1surgent+care+in+bengaluru!3m5!1s0x3bae3d6b24b1d2b5:0xfa514c97a07d1eab!8m2!3d13.0235045!4d77.5365502!16s%2Fg%2F11q8tk3mgr?entry=ttu&amp;g_ep=EgoyMDI2MDQxOS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>india</t>
-  </si>
-  <si>
-    <t>bengaluru</t>
-  </si>
-  <si>
-    <t>urgent-care</t>
-  </si>
-  <si>
-    <t>dry-run</t>
-  </si>
-  <si>
-    <t>auto-garage</t>
-  </si>
-  <si>
-    <t>2026-04-21 21:07:44</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -140,21 +43,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -479,139 +441,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="32" customWidth="1"/>
-    <col min="7" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="50" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="22" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="6"/>
+    <col width="28" customWidth="1" min="7" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>shop_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_website</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>generated_website</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>twitter</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>social_media_links</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>google_maps_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>build_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>template_used</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>deployed_at</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>website_url</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>30</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SHOP_BD5ABDA4EE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jai Hanuman Ambulance Service</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>097408 02690</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>info@jaihanumanambulance.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.jaihanumanambulance.com/</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Jai+Hanuman+Ambulance+Service/@13.023504,77.3923544,12z/data=!4m9!1m2!2m1!1surgent+care+in+bengaluru!3m5!1s0x3bae3d6b24b1d2b5:0xfa514c97a07d1eab!8m2!3d13.0235045!4d77.5365502!16s%2Fg%2F11q8tk3mgr?entry=ttu&amp;g_ep=EgoyMDI2MDQxOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>bengaluru</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>urgent-care</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>auto-garage</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-04-21 21:07:44</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>contains unreplaced template tokens</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>file:///C:/Users/Laptop/OneDrive/Desktop/Creative-client-/output/india/bengaluru/urgent-care/SHOP_BD5ABDA4EE/index.html</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>